--- a/www/download/IND.abstract_labour.empe.s.mv.rpA2.xlsx
+++ b/www/download/IND.abstract_labour.empe.s.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30034.484</t>
+          <t>30034483801.3797</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30758.439</t>
+          <t>30758439298.2037</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31345.963</t>
+          <t>31345962959.2553</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32814.976</t>
+          <t>32814976182.3413</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33911.1</t>
+          <t>33911099876.4105</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35377.632</t>
+          <t>35377632008.676</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35842.232</t>
+          <t>35842231915.2589</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37487.27</t>
+          <t>37487269701.2615</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>38848.048</t>
+          <t>38848048186.1347</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>39917.017</t>
+          <t>39917017328.4649</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>41370.845</t>
+          <t>41370844945.4478</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>42358.499</t>
+          <t>42358498667.6176</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>43507.854</t>
+          <t>43507854132.8086</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>47041.512</t>
+          <t>47041512298.6199</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>49600.33</t>
+          <t>49600329996.1911</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12947.243</t>
+          <t>12947242600.3897</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13080.836</t>
+          <t>13080835814.795</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13395.753</t>
+          <t>13395752846.4865</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13693.724</t>
+          <t>13693723869.9988</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14186.998</t>
+          <t>14186997793.6388</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14521.807</t>
+          <t>14521806696.6259</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14785.231</t>
+          <t>14785231257.3765</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14780.933</t>
+          <t>14780933351.8561</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14849.246</t>
+          <t>14849246396.1523</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15567.373</t>
+          <t>15567372960.6346</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>15506.723</t>
+          <t>15506723323.9186</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15568.428</t>
+          <t>15568428037.3616</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>15818.194</t>
+          <t>15818193824.1513</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>16212.247</t>
+          <t>16212246546.0126</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16013.256</t>
+          <t>16013256227.8617</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11309.589</t>
+          <t>11309589249.3109</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11480.778</t>
+          <t>11480778148.1867</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11789.315</t>
+          <t>11789315221.3805</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12150.817</t>
+          <t>12150817046.8161</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12489.084</t>
+          <t>12489084399.9549</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13113.578</t>
+          <t>13113577672.1064</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13477.287</t>
+          <t>13477286997.7591</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13533.133</t>
+          <t>13533132948.707</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13601.571</t>
+          <t>13601571389.2713</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14083.633</t>
+          <t>14083632715.3079</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14363.25</t>
+          <t>14363250211.5462</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14691.554</t>
+          <t>14691554428.7859</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>15033.817</t>
+          <t>15033817207.7353</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>15924.993</t>
+          <t>15924993498.8975</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>15822.846</t>
+          <t>15822846161.5346</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8659.622</t>
+          <t>8659622094.43547</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8849.866</t>
+          <t>8849866492.62314</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8255.237</t>
+          <t>8255237364.54658</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7453.187</t>
+          <t>7453186952.29475</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7330.092</t>
+          <t>7330092391.59612</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6938.993</t>
+          <t>6938992977.54725</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6894.592</t>
+          <t>6894592292.64027</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6900.87</t>
+          <t>6900869727.40751</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7417.691</t>
+          <t>7417690616.22153</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7985.091</t>
+          <t>7985091193.54572</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8247.723</t>
+          <t>8247723128.52662</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8628.73</t>
+          <t>8628729701.58754</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9079.974</t>
+          <t>9079973713.29417</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9493.609</t>
+          <t>9493609226.42173</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9436.079</t>
+          <t>9436078609.5811</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>226784.709</t>
+          <t>226784708525.954</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>226351.361</t>
+          <t>226351360988.465</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>233928.404</t>
+          <t>233928403582.439</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>235911.782</t>
+          <t>235911782335.975</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>246477.4</t>
+          <t>246477399663.155</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>261762.619</t>
+          <t>261762619341.279</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>269225.73</t>
+          <t>269225729702.965</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>283229.335</t>
+          <t>283229335263.231</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>293332.216</t>
+          <t>293332215804.951</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>311380.583</t>
+          <t>311380582729.519</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>322366.482</t>
+          <t>322366482484.178</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>340487.577</t>
+          <t>340487576741.11</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>356932.085</t>
+          <t>356932085230.814</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>371648.986</t>
+          <t>371648985611.936</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>383321.348</t>
+          <t>383321347820.615</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>67196.251</t>
+          <t>67196250636.0404</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>68238.638</t>
+          <t>68238638318.8073</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69394.057</t>
+          <t>69394056684.8441</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71086.962</t>
+          <t>71086961620.1977</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>73422.624</t>
+          <t>73422624196.3294</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>76221.594</t>
+          <t>76221594160.6591</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>77687.372</t>
+          <t>77687372419.4473</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78993.203</t>
+          <t>78993202871.7772</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>80787.601</t>
+          <t>80787601191.3044</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>83357.732</t>
+          <t>83357731837.8204</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85138.981</t>
+          <t>85138980926.4693</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>87313.766</t>
+          <t>87313766267.7553</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>89645.568</t>
+          <t>89645568078.9108</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>91437.193</t>
+          <t>91437192512.4405</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>89274.062</t>
+          <t>89274062208.7139</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>656428.681</t>
+          <t>656428680951.528</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>691775.642</t>
+          <t>691775641840.988</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>720833.875</t>
+          <t>720833874520.672</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>741849.87</t>
+          <t>741849870266.377</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>762893.004</t>
+          <t>762893003604.263</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>804505.778</t>
+          <t>804505777636.938</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>893957.669</t>
+          <t>893957669413.487</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>969424.582</t>
+          <t>969424582129.851</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1032270.001</t>
+          <t>1032270000821.43</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1083715.17</t>
+          <t>1083715169980.8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1136834.241</t>
+          <t>1136834241020.52</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1163237.036</t>
+          <t>1163237035981.59</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1202557.733</t>
+          <t>1202557732740.41</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1278790.54</t>
+          <t>1278790540475.34</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1329754.973</t>
+          <t>1329754973388.55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1259.107</t>
+          <t>1259107061.51497</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1287.727</t>
+          <t>1287726845.61323</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1271.419</t>
+          <t>1271418989.90307</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1254.068</t>
+          <t>1254067863.31904</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1299.603</t>
+          <t>1299602568.94916</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1344.853</t>
+          <t>1344852624.6595</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1404.363</t>
+          <t>1404362852.32562</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1454.305</t>
+          <t>1454304673.4056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1494.898</t>
+          <t>1494897672.57959</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1510.603</t>
+          <t>1510602893.34213</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1544.921</t>
+          <t>1544920898.84641</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1653.196</t>
+          <t>1653196098.57286</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1778.846</t>
+          <t>1778846015.84246</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1900.627</t>
+          <t>1900627045.29205</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1894.163</t>
+          <t>1894163317.44212</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23961.956</t>
+          <t>23961955879.9574</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23982.081</t>
+          <t>23982081343.2809</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23867.773</t>
+          <t>23867772796.7157</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23321.658</t>
+          <t>23321658173.0378</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22936.764</t>
+          <t>22936764049.3288</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22989.718</t>
+          <t>22989717807.2563</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22047.47</t>
+          <t>22047469745.7111</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21804.99</t>
+          <t>21804989768.7073</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21382.582</t>
+          <t>21382582146.416</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21977.889</t>
+          <t>21977889305.7677</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>22757.341</t>
+          <t>22757340552.5731</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>23271.421</t>
+          <t>23271420916.0776</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>23834.948</t>
+          <t>23834947904.5928</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>24521.95</t>
+          <t>24521949649.0631</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>24498.102</t>
+          <t>24498102011.8369</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>152626.778</t>
+          <t>152626778469.503</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>149686.573</t>
+          <t>149686573290.406</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>147749.545</t>
+          <t>147749545193.752</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>152743.584</t>
+          <t>152743583670.096</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>153268.943</t>
+          <t>153268942538.549</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>153432.002</t>
+          <t>153432002497.321</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>153567.009</t>
+          <t>153567009267.013</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>152743.391</t>
+          <t>152743391134.187</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>153789.216</t>
+          <t>153789216462.438</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>156618.972</t>
+          <t>156618971967.312</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>152689.596</t>
+          <t>152689595926.448</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>152127.096</t>
+          <t>152127096060.953</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>155489.58</t>
+          <t>155489579828.264</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>159418.922</t>
+          <t>159418921592.089</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>157162.936</t>
+          <t>157162935519.671</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10995.666</t>
+          <t>10995665596.6714</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11169.585</t>
+          <t>11169585224.3748</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11691.832</t>
+          <t>11691831756.3714</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12096.932</t>
+          <t>12096931631.4237</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12449.769</t>
+          <t>12449768592.676</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12684.215</t>
+          <t>12684214858.9601</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13010.61</t>
+          <t>13010610462.8407</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13093.636</t>
+          <t>13093635534.8352</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13187.68</t>
+          <t>13187679580.8513</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13282.533</t>
+          <t>13282532831.9816</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>13592.419</t>
+          <t>13592419335.123</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14083.573</t>
+          <t>14083573373.1963</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>13617.097</t>
+          <t>13617096909.3012</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>14312.605</t>
+          <t>14312605280.5315</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>13631.622</t>
+          <t>13631621574.4545</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>44364.495</t>
+          <t>44364494508.2998</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47437.137</t>
+          <t>47437136914.0448</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50777.452</t>
+          <t>50777451885.5923</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54604.612</t>
+          <t>54604612453.3128</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>58845.659</t>
+          <t>58845659139.3898</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>65335.509</t>
+          <t>65335509174.1696</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>68805.131</t>
+          <t>68805130510.5605</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>71287.221</t>
+          <t>71287220726.3601</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>73962.314</t>
+          <t>73962313623.7127</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>77475.764</t>
+          <t>77475763978.0602</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>82156.606</t>
+          <t>82156605560.3241</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>85742.292</t>
+          <t>85742291691.9742</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>88525.58</t>
+          <t>88525579727.0141</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>89817.263</t>
+          <t>89817263444.842</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>86787.594</t>
+          <t>86787594019.149</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4005.797</t>
+          <t>4005796598.29133</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3896.493</t>
+          <t>3896493252.88917</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3817.746</t>
+          <t>3817746289.58132</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3653.192</t>
+          <t>3653191669.12629</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3472.379</t>
+          <t>3472378714.18069</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3411.914</t>
+          <t>3411914232.09089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3542.587</t>
+          <t>3542587307.03132</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3627.156</t>
+          <t>3627155519.28362</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3624.67</t>
+          <t>3624669559.05486</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3676.039</t>
+          <t>3676039139.0154</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3966.192</t>
+          <t>3966191792.41626</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4162.5</t>
+          <t>4162499749.26263</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4154.365</t>
+          <t>4154365276.61429</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4156.065</t>
+          <t>4156064773.57205</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3637.532</t>
+          <t>3637531534.20196</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9828.598</t>
+          <t>9828597629.01739</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10046.13</t>
+          <t>10046130157.989</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10502.359</t>
+          <t>10502359039.7391</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10733.082</t>
+          <t>10733081569.3581</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11040.796</t>
+          <t>11040795549.3549</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11272.862</t>
+          <t>11272861560.7543</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11547.682</t>
+          <t>11547681826.5075</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11776.264</t>
+          <t>11776263871.3847</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11921.597</t>
+          <t>11921596677.7089</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12122.985</t>
+          <t>12122985318.9988</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>12305.104</t>
+          <t>12305103957.1567</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>12561.415</t>
+          <t>12561414589.4462</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>12985.209</t>
+          <t>12985209074.0564</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>13248.856</t>
+          <t>13248856002.4721</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>12828.123</t>
+          <t>12828122752.3703</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>88376.625</t>
+          <t>88376625418.184</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>90500.292</t>
+          <t>90500291639.8224</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>92664.633</t>
+          <t>92664633408.6266</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95498.934</t>
+          <t>95498933630.4529</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>99759.74</t>
+          <t>99759739735.2597</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>101798.397</t>
+          <t>101798397364.725</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>104443.251</t>
+          <t>104443251189.997</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>103469.416</t>
+          <t>103469415555.634</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>103355.437</t>
+          <t>103355437494.428</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>106242.68</t>
+          <t>106242679988.474</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>108489.02</t>
+          <t>108489020270.271</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>109665.262</t>
+          <t>109665262015.782</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>114074.023</t>
+          <t>114074023121.603</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>116658.385</t>
+          <t>116658385164.462</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>117280.61</t>
+          <t>117280609813.104</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>110480.522</t>
+          <t>110480521797.285</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>112830.116</t>
+          <t>112830116157.345</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>119313.886</t>
+          <t>119313885732.254</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>123829.211</t>
+          <t>123829210666.453</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>128120.457</t>
+          <t>128120456750.673</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>132213.611</t>
+          <t>132213611447.547</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>134878.911</t>
+          <t>134878911363.216</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>136576.707</t>
+          <t>136576706505.846</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>136199.787</t>
+          <t>136199787119.359</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>137880.881</t>
+          <t>137880880594.883</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>141052.462</t>
+          <t>141052462491.302</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>143453.526</t>
+          <t>143453525760.246</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>146418.808</t>
+          <t>146418807647.253</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>146760.154</t>
+          <t>146760153732.626</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>146249.485</t>
+          <t>146249485395.504</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13280.608</t>
+          <t>13280607944.1243</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13312.933</t>
+          <t>13312933437.7425</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13248.398</t>
+          <t>13248397944.5473</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14253.893</t>
+          <t>14253892697.0491</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14736.664</t>
+          <t>14736663972.6597</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>15045.827</t>
+          <t>15045827199.0276</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15317.653</t>
+          <t>15317652702.461</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16199.955</t>
+          <t>16199954846.7618</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>16591.934</t>
+          <t>16591934388.4224</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17802.858</t>
+          <t>17802858241.525</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17964.059</t>
+          <t>17964058940.2446</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>19590.071</t>
+          <t>19590070709.8496</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>19962.459</t>
+          <t>19962459220.4828</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>20328.421</t>
+          <t>20328421136.7522</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>19338.34</t>
+          <t>19338340021.2353</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18891.314</t>
+          <t>18891314287.4344</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18550.882</t>
+          <t>18550881553.5277</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18798.781</t>
+          <t>18798781387.8074</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19398.154</t>
+          <t>19398153890.544</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20720.044</t>
+          <t>20720043607.5542</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20125.041</t>
+          <t>20125041272.6442</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20585.69</t>
+          <t>20585689833.4447</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20905.488</t>
+          <t>20905487990.4635</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21304.468</t>
+          <t>21304468374.2492</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21718.616</t>
+          <t>21718615657.8115</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>22107.74</t>
+          <t>22107740032.8802</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>22535.179</t>
+          <t>22535179148.9698</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>22644.38</t>
+          <t>22644380214.2899</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>22871.051</t>
+          <t>22871050979.1999</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>22499.311</t>
+          <t>22499310744.8628</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>89137.042</t>
+          <t>89137042317.8424</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>97248.503</t>
+          <t>97248502951.1642</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>102136.486</t>
+          <t>102136485998.551</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>108225.027</t>
+          <t>108225026529.174</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>127347.364</t>
+          <t>127347363834.768</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>123022.665</t>
+          <t>123022665380.477</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>125434.852</t>
+          <t>125434852188.168</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>130449.392</t>
+          <t>130449391560.906</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>128890.311</t>
+          <t>128890311133.155</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>137690.037</t>
+          <t>137690037194.618</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>119193.009</t>
+          <t>119193008715.352</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>118768.352</t>
+          <t>118768351571.475</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>118035.19</t>
+          <t>118035189827.748</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>120291.597</t>
+          <t>120291596630.493</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>125255.322</t>
+          <t>125255321572.816</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>724374.95</t>
+          <t>724374949961.678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>751278.636</t>
+          <t>751278635947.987</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>768765.76</t>
+          <t>768765759575.185</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>781972.937</t>
+          <t>781972937316.47</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>787610.208</t>
+          <t>787610208059.498</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>827047.185</t>
+          <t>827047185336.012</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>863726.843</t>
+          <t>863726843159.004</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>866385.64</t>
+          <t>866385639660.235</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>912660.827</t>
+          <t>912660827108.099</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>935152.238</t>
+          <t>935152238296.112</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>941870.737</t>
+          <t>941870737101.403</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>934580.046</t>
+          <t>934580045795.607</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>917181.712</t>
+          <t>917181711566.515</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>932926.304</t>
+          <t>932926304385.061</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>946031.897</t>
+          <t>946031896864.067</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5539.961</t>
+          <t>5539961175.11778</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6014.547</t>
+          <t>6014547394.4564</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6303.788</t>
+          <t>6303788376.54905</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6892.094</t>
+          <t>6892094361.80388</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7424.818</t>
+          <t>7424817813.50702</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7808.829</t>
+          <t>7808828558.61755</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8164.859</t>
+          <t>8164858565.0587</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8545.788</t>
+          <t>8545788402.00746</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8879.924</t>
+          <t>8879923823.51663</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>9315.302</t>
+          <t>9315302063.09694</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10007.818</t>
+          <t>10007817569.5626</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>10658.007</t>
+          <t>10658006651.1783</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>11084.243</t>
+          <t>11084242843.642</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>11093.282</t>
+          <t>11093281868.5659</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10443.215</t>
+          <t>10443214984.9506</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>53835.941</t>
+          <t>53835941357.0138</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55955.304</t>
+          <t>55955303563.4254</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57484.22</t>
+          <t>57484220475.0143</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60029.99</t>
+          <t>60029989721.8908</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>62589.328</t>
+          <t>62589328302.789</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>64990.917</t>
+          <t>64990917290.373</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>65443.461</t>
+          <t>65443461476.0625</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>67219.272</t>
+          <t>67219272307.8071</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>69257.77</t>
+          <t>69257769893.7489</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>70265.419</t>
+          <t>70265418723.5347</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>72994.675</t>
+          <t>72994674749.8197</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>75789.527</t>
+          <t>75789527095.9692</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>78140.801</t>
+          <t>78140800840.3513</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>81315.855</t>
+          <t>81315855281.0302</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>78922.703</t>
+          <t>78922702805.6555</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>312098.758</t>
+          <t>312098757701.117</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>319298.673</t>
+          <t>319298673481.342</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>321778.316</t>
+          <t>321778315605.456</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>320196.403</t>
+          <t>320196402983.616</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>317216.016</t>
+          <t>317216015719.813</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>325459.274</t>
+          <t>325459273541.27</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>328030.508</t>
+          <t>328030507924.08</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>325323.565</t>
+          <t>325323564853.173</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>331379.488</t>
+          <t>331379488395.548</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>334499.234</t>
+          <t>334499233548.775</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>332380.295</t>
+          <t>332380294771.953</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>341349.775</t>
+          <t>341349774818.964</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>342869.261</t>
+          <t>342869261420.213</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>334576.527</t>
+          <t>334576527346.378</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>308976.948</t>
+          <t>308976947775.952</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>107587.848</t>
+          <t>107587847615.741</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>110210.768</t>
+          <t>110210768069.151</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>113195.824</t>
+          <t>113195824177.147</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>108580.453</t>
+          <t>108580452929.902</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>116523.088</t>
+          <t>116523088354.797</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>120904.358</t>
+          <t>120904357624.113</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>125677.302</t>
+          <t>125677302068.992</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>134667.123</t>
+          <t>134667122765.664</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>138103.295</t>
+          <t>138103294944.517</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>149212.454</t>
+          <t>149212454378.306</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>149406.411</t>
+          <t>149406410965.512</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>152267.149</t>
+          <t>152267148628.986</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>151525.002</t>
+          <t>151525001712.646</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>152449.565</t>
+          <t>152449565428.506</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>151990.516</t>
+          <t>151990516310.841</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7260.148</t>
+          <t>7260148032.48465</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6975.781</t>
+          <t>6975781100.40018</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6914.235</t>
+          <t>6914234869.87965</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7036.463</t>
+          <t>7036463052.31785</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6841.408</t>
+          <t>6841408027.0293</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7132.922</t>
+          <t>7132922456.96746</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6849.089</t>
+          <t>6849089073.23472</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6994.645</t>
+          <t>6994645132.69216</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7199.257</t>
+          <t>7199256878.75401</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7552.973</t>
+          <t>7552972837.81307</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8256.131</t>
+          <t>8256131346.79825</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8497.122</t>
+          <t>8497122248.69701</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9115.301</t>
+          <t>9115301199.79553</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9575.259</t>
+          <t>9575258875.69074</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8885.531</t>
+          <t>8885531361.91987</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>821.438</t>
+          <t>821437534.149532</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>834.824</t>
+          <t>834823648.835424</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>883.108</t>
+          <t>883107953.05361</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>945.984</t>
+          <t>945983957.736159</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1037.442</t>
+          <t>1037442343.0138</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1101.623</t>
+          <t>1101623395.11124</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1153.924</t>
+          <t>1153923857.33742</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1190.398</t>
+          <t>1190397751.26392</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1098.577</t>
+          <t>1098577448.94576</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1347.788</t>
+          <t>1347788300.24338</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1422.705</t>
+          <t>1422704738.36004</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1421.244</t>
+          <t>1421244277.45615</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1542.882</t>
+          <t>1542882401.17817</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1647.335</t>
+          <t>1647334995.56281</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1822.79</t>
+          <t>1822790074.54833</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4475.52</t>
+          <t>4475519546.60061</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4477.715</t>
+          <t>4477715166.1819</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4338.94</t>
+          <t>4338939795.8599</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4453.199</t>
+          <t>4453198552.6365</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4452.791</t>
+          <t>4452790592.16861</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4451.618</t>
+          <t>4451618282.2319</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4378.827</t>
+          <t>4378826708.10464</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4438.993</t>
+          <t>4438992641.60817</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4409.347</t>
+          <t>4409346597.63663</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4629.963</t>
+          <t>4629962954.16299</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4778.365</t>
+          <t>4778365298.0348</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4972.439</t>
+          <t>4972438590.55133</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5267.636</t>
+          <t>5267636479.28361</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5343.239</t>
+          <t>5343239196.61881</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4620.297</t>
+          <t>4620296754.79276</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>104872.503</t>
+          <t>104872503030.034</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>109777.856</t>
+          <t>109777856119.901</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>117171.262</t>
+          <t>117171262020.542</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>119524.316</t>
+          <t>119524316351.23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>124051.601</t>
+          <t>124051600987.441</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>129163.727</t>
+          <t>129163726950.125</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>133100.797</t>
+          <t>133100796901.915</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>136042.574</t>
+          <t>136042574153.453</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>139826.245</t>
+          <t>139826245489.659</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>147853.249</t>
+          <t>147853249292.128</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>153512.753</t>
+          <t>153512753127.379</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>156199.955</t>
+          <t>156199954798.109</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>158764.32</t>
+          <t>158764319542.08</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>170165.48</t>
+          <t>170165480373.708</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>167991.262</t>
+          <t>167991261881.528</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>441.039</t>
+          <t>441038708.5766</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>445.074</t>
+          <t>445074055.750719</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>433.863</t>
+          <t>433862869.081594</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>426.94</t>
+          <t>426939703.638402</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>438.041</t>
+          <t>438041476.220208</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>446.232</t>
+          <t>446232385.027447</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>388.332</t>
+          <t>388332410.868854</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>461.261</t>
+          <t>461261338.430849</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>465.655</t>
+          <t>465655035.103148</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>499.741</t>
+          <t>499741448.784071</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>506.296</t>
+          <t>506295592.27042</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>521.353</t>
+          <t>521353496.345582</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>543.777</t>
+          <t>543776767.204529</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>566.494</t>
+          <t>566493582.379361</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>574.758</t>
+          <t>574758407.740725</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>23888.886</t>
+          <t>23888885685.0862</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>24969.086</t>
+          <t>24969085969.7003</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26335.354</t>
+          <t>26335353675.7909</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>27205.387</t>
+          <t>27205387354.8805</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>29604.721</t>
+          <t>29604720908.1554</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>28208.825</t>
+          <t>28208824599.3283</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28604.953</t>
+          <t>28604953260.7237</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29471.981</t>
+          <t>29471981283.6663</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30480.622</t>
+          <t>30480622087.9677</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30947.025</t>
+          <t>30947025366.2657</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>31295.468</t>
+          <t>31295467533.7382</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>31846.028</t>
+          <t>31846028145.5786</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>32890.074</t>
+          <t>32890074440.9188</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>33451.332</t>
+          <t>33451331925.5541</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>33109.055</t>
+          <t>33109054998.3605</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>44013.483</t>
+          <t>44013482699.0598</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>44132.228</t>
+          <t>44132228299.4231</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44957.824</t>
+          <t>44957823762.591</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>45465.596</t>
+          <t>45465596492.6556</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>46879.921</t>
+          <t>46879920871.2262</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>48498.432</t>
+          <t>48498432380.2937</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>52739.086</t>
+          <t>52739085691.84</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>51798.341</t>
+          <t>51798341308.2261</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>53539.709</t>
+          <t>53539709130.8785</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>56243.832</t>
+          <t>56243832235.506</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>58621.768</t>
+          <t>58621768007.6028</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>62163.465</t>
+          <t>62163464900.5211</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>65889.368</t>
+          <t>65889367914.8766</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>68468.894</t>
+          <t>68468893855.9118</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>69394.773</t>
+          <t>69394772823.5804</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11466.853</t>
+          <t>11466852556.0648</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11540.668</t>
+          <t>11540667867.0596</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11282.08</t>
+          <t>11282080323.5854</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11171.181</t>
+          <t>11171181398.4715</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11708.894</t>
+          <t>11708894025.2688</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12052.73</t>
+          <t>12052729720.9094</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12295.083</t>
+          <t>12295083240.898</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12585.838</t>
+          <t>12585838050.7575</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12899.051</t>
+          <t>12899051163.8913</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13717.608</t>
+          <t>13717608456.4127</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13961.581</t>
+          <t>13961581075.8672</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>15153.845</t>
+          <t>15153845232.3605</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>15479.699</t>
+          <t>15479698553.9747</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>15869.918</t>
+          <t>15869917638.3535</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>16001.236</t>
+          <t>16001235809.1305</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18752.967</t>
+          <t>18752966737.1521</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19111.714</t>
+          <t>19111714020.193</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17189.767</t>
+          <t>17189767247.085</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16239.503</t>
+          <t>16239502791.9404</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18784.764</t>
+          <t>18784764338.903</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18818.852</t>
+          <t>18818852028.7925</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18693.458</t>
+          <t>18693457687.7317</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>20066.053</t>
+          <t>20066053330.922</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>20485.958</t>
+          <t>20485957641.6687</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22668.043</t>
+          <t>22668043476.1097</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22389.14</t>
+          <t>22389140102.1473</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>23441.068</t>
+          <t>23441067999.4729</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>23652.025</t>
+          <t>23652024984.6023</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>24549.933</t>
+          <t>24549932964.924</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>25473.943</t>
+          <t>25473942591.0014</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>335781.399</t>
+          <t>335781399394.215</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>332782.847</t>
+          <t>332782847205.344</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>328446.954</t>
+          <t>328446954449.544</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>315644.42</t>
+          <t>315644420407.63</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>317532.471</t>
+          <t>317532470945.696</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>321707.796</t>
+          <t>321707795844.355</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>325083.733</t>
+          <t>325083732736.718</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>327316.145</t>
+          <t>327316144845.255</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>328352.704</t>
+          <t>328352704027.464</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>335674.444</t>
+          <t>335674443865.519</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>342599.32</t>
+          <t>342599320379.879</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>345990.116</t>
+          <t>345990116386.69</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>350729.476</t>
+          <t>350729475505.576</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>325305.661</t>
+          <t>325305661305.748</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>317480.682</t>
+          <t>317480682488.133</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10200.341</t>
+          <t>10200341163.816</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10154.712</t>
+          <t>10154712019.4986</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10063.423</t>
+          <t>10063422685.3314</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9915.715</t>
+          <t>9915714679.59419</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9559.875</t>
+          <t>9559874799.70298</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9422.852</t>
+          <t>9422851842.79713</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9397.561</t>
+          <t>9397560886.59088</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9206.153</t>
+          <t>9206153402.26368</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8979.272</t>
+          <t>8979271632.63144</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9094.759</t>
+          <t>9094758638.366</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9528.488</t>
+          <t>9528488127.79162</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>9688.739</t>
+          <t>9688738712.83564</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>9985.335</t>
+          <t>9985335313.17952</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>10167.966</t>
+          <t>10167966372.4518</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>9702.135</t>
+          <t>9702135319.77873</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3729.35</t>
+          <t>3729350325.30531</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3696.683</t>
+          <t>3696682753.13597</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3619.583</t>
+          <t>3619582783.67547</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3627.475</t>
+          <t>3627475456.62517</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3754.211</t>
+          <t>3754210869.67031</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3875.521</t>
+          <t>3875520869.61024</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3758.877</t>
+          <t>3758876823.51186</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3889.676</t>
+          <t>3889676112.17715</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4061.705</t>
+          <t>4061705149.05249</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4146.25</t>
+          <t>4146249514.97753</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4219.358</t>
+          <t>4219358056.48926</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>4376.403</t>
+          <t>4376402994.42602</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>4532.55</t>
+          <t>4532550413.83984</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>4677.605</t>
+          <t>4677605466.84445</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4635.639</t>
+          <t>4635639169.68335</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17890.634</t>
+          <t>17890633745.0371</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18017.915</t>
+          <t>18017914859.0517</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17993.02</t>
+          <t>17993020281.6308</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>18393.775</t>
+          <t>18393774799.9964</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19130.936</t>
+          <t>19130935709.2592</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20516.981</t>
+          <t>20516981019.5007</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21079.649</t>
+          <t>21079649060.9682</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20926.241</t>
+          <t>20926240525.884</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20809.824</t>
+          <t>20809824375.2228</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>21231.733</t>
+          <t>21231732795.7717</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21490.264</t>
+          <t>21490263973.8835</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>22161.587</t>
+          <t>22161586906.6503</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>23163.402</t>
+          <t>23163401837.4966</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>23770.924</t>
+          <t>23770924364.4458</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>23115.416</t>
+          <t>23115416117.2485</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>39680.608</t>
+          <t>39680608026.8699</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>42135.676</t>
+          <t>42135676434.5972</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>43213.147</t>
+          <t>43213146757.411</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>42440.941</t>
+          <t>42440940761.7936</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>42560.518</t>
+          <t>42560517809.8508</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45488.631</t>
+          <t>45488630695.559</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>45435.794</t>
+          <t>45435794091.9787</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>48147.304</t>
+          <t>48147303842.5853</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>49938.286</t>
+          <t>49938285689.8038</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>48908.677</t>
+          <t>48908676733.6335</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>53457.764</t>
+          <t>53457764257.9839</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>54522.285</t>
+          <t>54522285202.1379</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>55482.028</t>
+          <t>55482028319.7674</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>57691.325</t>
+          <t>57691325215.7909</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>58404.435</t>
+          <t>58404435085.5972</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>39219.689</t>
+          <t>39219689423.1092</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>39869.591</t>
+          <t>39869590771.5793</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41429.256</t>
+          <t>41429255576.9393</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42108.065</t>
+          <t>42108064795.8183</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>43352.435</t>
+          <t>43352435038.8068</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45030.992</t>
+          <t>45030991889.2268</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>43527.85</t>
+          <t>43527849965.9704</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>44776.561</t>
+          <t>44776561461.617</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>46455.288</t>
+          <t>46455288461.0161</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>48918.635</t>
+          <t>48918635036.6225</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>51083.668</t>
+          <t>51083667960.77</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>53132.66</t>
+          <t>53132660443.5033</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>55394.679</t>
+          <t>55394678702.1454</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>58154.904</t>
+          <t>58154904495.3765</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>58793.329</t>
+          <t>58793329411.3972</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>729360.132</t>
+          <t>729360131673.022</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>747143.006</t>
+          <t>747143005922.891</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>768803.268</t>
+          <t>768803267695.24</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>796112.628</t>
+          <t>796112628242.348</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>814732.484</t>
+          <t>814732484437.233</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>835936.668</t>
+          <t>835936668353.144</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>827065.706</t>
+          <t>827065705881.27</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>818209.817</t>
+          <t>818209817259.862</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>818504.646</t>
+          <t>818504645986.804</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>835202.794</t>
+          <t>835202794097.534</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>852211.727</t>
+          <t>852211726666.561</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>874884.567</t>
+          <t>874884567037.148</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>889685.078</t>
+          <t>889685077707.705</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>891913.841</t>
+          <t>891913840629.426</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>857821.762</t>
+          <t>857821762169.447</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1436628.247</t>
+          <t>1436628246559.58</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1504599.937</t>
+          <t>1504599936782.95</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1555189.366</t>
+          <t>1555189365782.58</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1567109.236</t>
+          <t>1567109235877.95</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1591332.636</t>
+          <t>1591332636125.75</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1677104.478</t>
+          <t>1677104478405.96</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1777161.598</t>
+          <t>1777161598121.12</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1832414.064</t>
+          <t>1832414063870.6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1953906.528</t>
+          <t>1953906527647.76</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2107370.116</t>
+          <t>2107370116123.57</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2179239.207</t>
+          <t>2179239207054.3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2282643.488</t>
+          <t>2282643488064.36</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2400376.415</t>
+          <t>2400376415498.68</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2554854.256</t>
+          <t>2554854256471.92</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2647864.052</t>
+          <t>2647864051719.06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5612489.778</t>
+          <t>5612489778017.99</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5793907.255</t>
+          <t>5793907255123.12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5950575.27</t>
+          <t>5950575270342.24</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6040066.365</t>
+          <t>6040066364708.29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6181827.089</t>
+          <t>6181827088534.49</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6430288.059</t>
+          <t>6430288059382.79</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6688212.613</t>
+          <t>6688212612842.19</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6857814.678</t>
+          <t>6857814677982.02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7128505.247</t>
+          <t>7128505247247.53</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>7458458.734</t>
+          <t>7458458734041.13</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>7636880.653</t>
+          <t>7636880652971.65</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>7846160.34</t>
+          <t>7846160339939.15</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8057390.774</t>
+          <t>8057390773660.85</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8333370.878</t>
+          <t>8333370877641.31</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8426342.408</t>
+          <t>8426342407614.12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.empe.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
